--- a/output/pdf_financials_xlsx/MASS.xlsx
+++ b/output/pdf_financials_xlsx/MASS.xlsx
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.023537</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.049914</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.000168</v>
@@ -5704,43 +5704,43 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.289961</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.289961</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.507892</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.8558480000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.068582</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.088782</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.088782</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.42022</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.57512</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.61162</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.811504</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.811504</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.902068</v>
       </c>
     </row>
     <row r="93">
@@ -9306,7 +9306,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10066,7 +10070,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10982,7 +10990,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -12110,7 +12122,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -45340,12 +45356,16 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E394" s="5" t="n">
-        <v>-0.023537</v>
+        <v>0.023537</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>-0.049914</v>
+        <v>0.049914</v>
       </c>
       <c r="G394" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MASS.xlsx
+++ b/output/pdf_financials_xlsx/MASS.xlsx
@@ -1008,40 +1008,40 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002672</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005691</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011998</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.013117</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000337</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000577</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000606</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000256</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>6.8e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00084</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00151</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1917,40 +1917,40 @@
         <v>-0.010168</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.33146</v>
+        <v>-0.334132</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.184527</v>
+        <v>-0.190218</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.366916</v>
+        <v>-0.378914</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.865322</v>
+        <v>-0.878439</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.852084</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-6.949325</v>
+        <v>-6.949662</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.883954</v>
+        <v>-0.884531</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.850571</v>
+        <v>-0.851177</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.962431</v>
+        <v>-2.962687</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.626727</v>
+        <v>-0.626795</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.921336</v>
+        <v>-0.922176</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.359772</v>
+        <v>-0.361282</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.904124</v>
@@ -2027,40 +2027,40 @@
         <v>-0.010168</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.33146</v>
+        <v>-0.334132</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.184527</v>
+        <v>-0.190218</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.366916</v>
+        <v>-0.378914</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.865322</v>
+        <v>-0.878439</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.852084</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-6.949325</v>
+        <v>-6.949662</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.883954</v>
+        <v>-0.884531</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.850571</v>
+        <v>-0.851177</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.962431</v>
+        <v>-2.962687</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.626727</v>
+        <v>-0.626795</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.921336</v>
+        <v>-0.922176</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.359772</v>
+        <v>-0.361282</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.904124</v>
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.16179</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.015076</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.519832</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.029771</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.875449</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>1.830459</v>
@@ -2340,13 +2340,13 @@
         <v>0.07001599999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.012779</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.00489</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.00579</v>
       </c>
     </row>
     <row r="35">
@@ -2411,19 +2411,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.16179</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.015076</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.519832</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.029771</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.875449</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>1.830459</v>
@@ -2450,13 +2450,13 @@
         <v>0.07001599999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.012779</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.00489</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.00579</v>
       </c>
     </row>
     <row r="37">
@@ -3071,19 +3071,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.368255</v>
+        <v>0.206465</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.015076</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.519832</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.059771</v>
+        <v>0.03</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.9054489999999999</v>
+        <v>0.03</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.148902</v>
@@ -3110,13 +3110,13 @@
         <v>0.06614100000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.088616</v>
+        <v>0.075837</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.029523</v>
+        <v>0.024633</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.024071</v>
+        <v>0.018281</v>
       </c>
     </row>
     <row r="49">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -42766,7 +42766,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -44012,7 +44012,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">

--- a/output/pdf_financials_xlsx/MASS.xlsx
+++ b/output/pdf_financials_xlsx/MASS.xlsx
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1.356113</v>
+        <v>-0.553827</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.462919</v>
+        <v>-0.669758</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.010168</v>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-1.356113</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.462919</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -4212,40 +4212,40 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.012147</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.028387</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.06564399999999999</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.134658</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.208553</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.065524</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.051462</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.042929</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.065428</v>
       </c>
     </row>
     <row r="68">
@@ -4267,7 +4267,7 @@
         <v>0.009813000000000001</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.03929</v>
+        <v>0.051437</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.081148</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-1.90994</v>
+        <v>-0.553827</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-0.206839</v>
+        <v>-0.669758</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.010168</v>
@@ -6700,15 +6700,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0.007338</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0.004812</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -17626,7 +17622,11 @@
           <t>Shares issued for cash (net)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -23788,7 +23788,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -24946,7 +24950,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -26098,7 +26106,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
         <v>-0.553827</v>
       </c>
@@ -26290,7 +26302,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E192" s="5" t="n">
         <v>0.0009829999999999999</v>
       </c>
@@ -46128,7 +46144,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E402" s="5" t="n">
         <v>-0.553827</v>
       </c>
@@ -46224,7 +46244,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E403" s="5" t="n">
@@ -46606,7 +46626,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
         <v>-8e-08</v>
       </c>
